--- a/outputs/EISPOT_5mV_1,5A_#1.xlsx
+++ b/outputs/EISPOT_5mV_1,5A_#1.xlsx
@@ -423,29 +423,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Campo</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unidad</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Técnica</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -453,11 +459,12 @@
           <t>Potentiostatic EIS</t>
         </is>
       </c>
+      <c r="C2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Fecha</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -465,11 +472,12 @@
           <t>24/2/2026</t>
         </is>
       </c>
+      <c r="C3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Hora</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -477,6 +485,7 @@
           <t>4:05:28</t>
         </is>
       </c>
+      <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -487,55 +496,85 @@
       <c r="B5" s="2" t="n">
         <v>1.83302</v>
       </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>freqinit</t>
+          <t>Frecuencia inicial</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>100000</v>
       </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>freqfinal</t>
+          <t>Frecuencia final</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>0.1</v>
       </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ptsperdec</t>
+          <t>Puntos por década</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>10</v>
       </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>points/decade</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>vac</t>
+          <t>Amplitud</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>mV rms</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>Área</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>25</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>cm^2</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -549,11 +588,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -572,7 +611,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Frequency</t>
+          <t>Frecuencia</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -612,1959 +651,2007 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Temperatura</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>100078.1</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.0130899</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.006125</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.014452</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>25.07585</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>1.383188</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>1.830373</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>63.01017</v>
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>ohm</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ohm</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ohm</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>79453.13</v>
+        <v>100078.1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.012933</v>
+        <v>0.0130899</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.0049751</v>
+        <v>0.006125</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.0138569</v>
+        <v>0.014452</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>21.04082</v>
+        <v>25.07585</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1.383565</v>
+        <v>1.383188</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1.83043</v>
+        <v>1.830373</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>63.00355</v>
+        <v>63.01017</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>63140.62</v>
+        <v>79453.13</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.0127983</v>
+        <v>0.012933</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.0040322</v>
+        <v>0.0049751</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.0134184</v>
+        <v>0.0138569</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>17.48732</v>
+        <v>21.04082</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1.382847</v>
+        <v>1.383565</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1.830418</v>
+        <v>1.83043</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>63.00608</v>
+        <v>63.00355</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>50203.12</v>
+        <v>63140.62</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.0126878</v>
+        <v>0.0127983</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.0032682</v>
+        <v>0.0040322</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.0131019</v>
+        <v>0.0134184</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>14.44466</v>
+        <v>17.48732</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1.382751</v>
+        <v>1.382847</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1.830423</v>
+        <v>1.830418</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>63.01151</v>
+        <v>63.00608</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>39890.62</v>
+        <v>50203.12</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.0125982</v>
+        <v>0.0126878</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.0026388</v>
+        <v>0.0032682</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.0128716</v>
+        <v>0.0131019</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>11.83019</v>
+        <v>14.44466</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1.381099</v>
+        <v>1.382751</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1.830423</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>63.01033</v>
+        <v>63.01151</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>31640.63</v>
+        <v>39890.62</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.0125294</v>
+        <v>0.0125982</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.0021188</v>
+        <v>0.0026388</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.0127073</v>
+        <v>0.0128716</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>9.598470000000001</v>
+        <v>11.83019</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.379981</v>
+        <v>1.381099</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1.830431</v>
+        <v>1.830423</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>63.01907</v>
+        <v>63.01033</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>25171.88</v>
+        <v>31640.63</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.0124759</v>
+        <v>0.0125294</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.0016995</v>
+        <v>0.0021188</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.0125911</v>
+        <v>0.0127073</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>7.757132</v>
+        <v>9.598470000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1.380742</v>
+        <v>1.379981</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1.830419</v>
+        <v>1.830431</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>63.01046</v>
+        <v>63.01907</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>20015.62</v>
+        <v>25171.88</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.0124352</v>
+        <v>0.0124759</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.0013557</v>
+        <v>0.0016995</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.0125089</v>
+        <v>0.0125911</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>6.221966</v>
+        <v>7.757132</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1.380002</v>
+        <v>1.380742</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1.830424</v>
+        <v>1.830419</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>63.01491</v>
+        <v>63.01046</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>15890.62</v>
+        <v>20015.62</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.0124047</v>
+        <v>0.0124352</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.0010719</v>
+        <v>0.0013557</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.012451</v>
+        <v>0.0125089</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4.938788</v>
+        <v>6.221966</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.379481</v>
+        <v>1.380002</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1.830414</v>
+        <v>1.830424</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>63.02632</v>
+        <v>63.01491</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>12609.38</v>
+        <v>15890.62</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.0123811</v>
+        <v>0.0124047</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.000839</v>
+        <v>0.0010719</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.0124095</v>
+        <v>0.012451</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>3.876922</v>
+        <v>4.938788</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1.379058</v>
+        <v>1.379481</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1.830428</v>
+        <v>1.830414</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>63.03142</v>
+        <v>63.02632</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>10078.13</v>
+        <v>12609.38</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.0123686</v>
+        <v>0.0123811</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.0006474</v>
+        <v>0.000839</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.0123855</v>
+        <v>0.0124095</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2.996099</v>
+        <v>3.876922</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1.378048</v>
+        <v>1.379058</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1.830415</v>
+        <v>1.830428</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>63.02988</v>
+        <v>63.03142</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>8015.625</v>
+        <v>10078.13</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.0123609</v>
+        <v>0.0123686</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.000487</v>
+        <v>0.0006474</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.0123705</v>
+        <v>0.0123855</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>2.256082</v>
+        <v>2.996099</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1.378031</v>
+        <v>1.378048</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1.830419</v>
+        <v>1.830415</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>63.01591</v>
+        <v>63.02988</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>6328.125</v>
+        <v>8015.625</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.0123577</v>
+        <v>0.0123609</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.0003449</v>
+        <v>0.000487</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.0123625</v>
+        <v>0.0123705</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1.598787</v>
+        <v>2.256082</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.37796</v>
+        <v>1.378031</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1.830429</v>
+        <v>1.830419</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>63.03258</v>
+        <v>63.01591</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>5015.625</v>
+        <v>6328.125</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.0123529</v>
+        <v>0.0123577</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.0002252</v>
+        <v>0.0003449</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.012355</v>
+        <v>0.0123625</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1.044386</v>
+        <v>1.598787</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1.378394</v>
+        <v>1.37796</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1.83043</v>
+        <v>1.830429</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>63.02588</v>
+        <v>63.03258</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3984.375</v>
+        <v>5015.625</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.0123623</v>
+        <v>0.0123529</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.0001189</v>
+        <v>0.0002252</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.0123629</v>
+        <v>0.012355</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.5509302</v>
+        <v>1.044386</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1.376496</v>
+        <v>1.378394</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1.830409</v>
+        <v>1.83043</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>63.0329</v>
+        <v>63.02588</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>3170.956</v>
+        <v>3984.375</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.0123736</v>
+        <v>0.0123623</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2.202885e-05</v>
+        <v>0.0001189</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.0123736</v>
+        <v>0.0123629</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.1020046</v>
+        <v>0.5509302</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1.377032</v>
+        <v>1.376496</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1.830437</v>
+        <v>1.830409</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>63.02149</v>
+        <v>63.0329</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2527.573</v>
+        <v>3170.956</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0.0123839</v>
+        <v>0.0123736</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-6.81228e-05</v>
+        <v>2.202885e-05</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.0123841</v>
+        <v>0.0123736</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-0.3151767</v>
+        <v>0.1020046</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1.375635</v>
+        <v>1.377032</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1.830406</v>
+        <v>1.830437</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>63.02235</v>
+        <v>63.02149</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1976.103</v>
+        <v>2527.573</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.0124026</v>
+        <v>0.0123839</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>-0.0001694</v>
+        <v>-6.81228e-05</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.0124038</v>
+        <v>0.0123841</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.7824962</v>
+        <v>-0.3151767</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1.37624</v>
+        <v>1.375635</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1.830431</v>
+        <v>1.830406</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>63.03372</v>
+        <v>63.02235</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1577.524</v>
+        <v>1976.103</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.0124254</v>
+        <v>0.0124026</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>-0.0002592</v>
+        <v>-0.0001694</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.0124281</v>
+        <v>0.0124038</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-1.194914</v>
+        <v>-0.7824962</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1.375236</v>
+        <v>1.37624</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1.830416</v>
+        <v>1.830431</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>63.03284</v>
+        <v>63.03372</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1265.625</v>
+        <v>1577.524</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.0124491</v>
+        <v>0.0124254</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>-0.0003535</v>
+        <v>-0.0002592</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.0124541</v>
+        <v>0.0124281</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-1.626713</v>
+        <v>-1.194914</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1.375263</v>
+        <v>1.375236</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1.830423</v>
+        <v>1.830416</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>63.0211</v>
+        <v>63.03284</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>998.264</v>
+        <v>1265.625</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.0124842</v>
+        <v>0.0124491</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>-0.0004637</v>
+        <v>-0.0003535</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.0124928</v>
+        <v>0.0124541</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-2.127082</v>
+        <v>-1.626713</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1.374505</v>
+        <v>1.375263</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1.830427</v>
+        <v>1.830423</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>63.02571</v>
+        <v>63.0211</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>796.875</v>
+        <v>998.264</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.0125192</v>
+        <v>0.0124842</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>-0.0005766</v>
+        <v>-0.0004637</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.0125325</v>
+        <v>0.0124928</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-2.637074</v>
+        <v>-2.127082</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1.374024</v>
+        <v>1.374505</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1.830413</v>
+        <v>1.830427</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>63.02061</v>
+        <v>63.02571</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>627.7902</v>
+        <v>796.875</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.0125686</v>
+        <v>0.0125192</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>-0.0007141</v>
+        <v>-0.0005766</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.0125889</v>
+        <v>0.0125325</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-3.251612</v>
+        <v>-2.637074</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1.372987</v>
+        <v>1.374024</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1.830404</v>
+        <v>1.830413</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>63.04015</v>
+        <v>63.02061</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>505.5147</v>
+        <v>627.7902</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.0126135</v>
+        <v>0.0125686</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>-0.0008708</v>
+        <v>-0.0007141</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.0126435</v>
+        <v>0.0125889</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-3.949417</v>
+        <v>-3.251612</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1.373965</v>
+        <v>1.372987</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1.830407</v>
+        <v>1.830404</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>63.02591</v>
+        <v>63.04015</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>397.9953</v>
+        <v>505.5147</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.0126735</v>
+        <v>0.0126135</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>-0.0010635</v>
+        <v>-0.0008708</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.0127181</v>
+        <v>0.0126435</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-4.796888</v>
+        <v>-3.949417</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1.373563</v>
+        <v>1.373965</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1.830417</v>
+        <v>1.830407</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>63.02032</v>
+        <v>63.02591</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>315.5048</v>
+        <v>397.9953</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0.0127432</v>
+        <v>0.0126735</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>-0.0012933</v>
+        <v>-0.0010635</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.0128086</v>
+        <v>0.0127181</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-5.794996</v>
+        <v>-4.796888</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>1.373365</v>
+        <v>1.373563</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1.830416</v>
+        <v>1.830417</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>63.02541</v>
+        <v>63.02032</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>252.4038</v>
+        <v>315.5048</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0.0128235</v>
+        <v>0.0127432</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>-0.001561</v>
+        <v>-0.0012933</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.0129182</v>
+        <v>0.0128086</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-6.940371</v>
+        <v>-5.794996</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>1.372881</v>
+        <v>1.373365</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1.830419</v>
+        <v>1.830416</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>63.02213</v>
+        <v>63.02541</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>198.6229</v>
+        <v>252.4038</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.0129323</v>
+        <v>0.0128235</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>-0.0019053</v>
+        <v>-0.001561</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.0130719</v>
+        <v>0.0129182</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>-8.381237</v>
+        <v>-6.940371</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>1.372567</v>
+        <v>1.372881</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1.830421</v>
+        <v>1.830419</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>63.01634</v>
+        <v>63.02213</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>158.3615</v>
+        <v>198.6229</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.013063</v>
+        <v>0.0129323</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>-0.0023045</v>
+        <v>-0.0019053</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.0132648</v>
+        <v>0.0130719</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>-10.00474</v>
+        <v>-8.381237</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1.37183</v>
+        <v>1.372567</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1.830419</v>
+        <v>1.830421</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>63.01242</v>
+        <v>63.01634</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>125.558</v>
+        <v>158.3615</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.0132347</v>
+        <v>0.013063</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>-0.0027964</v>
+        <v>-0.0023045</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.0135269</v>
+        <v>0.0132648</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>-11.93069</v>
+        <v>-10.00474</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>1.371487</v>
+        <v>1.37183</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1.830391</v>
+        <v>1.830419</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>63.02933</v>
+        <v>63.01242</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>100.4464</v>
+        <v>125.558</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.0134497</v>
+        <v>0.0132347</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>-0.0033671</v>
+        <v>-0.0027964</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.0138647</v>
+        <v>0.0135269</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>-14.05519</v>
+        <v>-11.93069</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1.371356</v>
+        <v>1.371487</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1.830419</v>
+        <v>1.830391</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>63.0141</v>
+        <v>63.02933</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>79.00281</v>
+        <v>100.4464</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.0137596</v>
+        <v>0.0134497</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>-0.0041041</v>
+        <v>-0.0033671</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.0143586</v>
+        <v>0.0138647</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>-16.60816</v>
+        <v>-14.05519</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>1.370025</v>
+        <v>1.371356</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1.830402</v>
+        <v>1.830419</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>63.01006</v>
+        <v>63.0141</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>63.3446</v>
+        <v>79.00281</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.0141407</v>
+        <v>0.0137596</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>-0.0049095</v>
+        <v>-0.0041041</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.0149687</v>
+        <v>0.0143586</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>-19.14631</v>
+        <v>-16.60816</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1.370197</v>
+        <v>1.370025</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1.830424</v>
+        <v>1.830402</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>63.02205</v>
+        <v>63.01006</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>50.22321</v>
+        <v>63.3446</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0.0146794</v>
+        <v>0.0141407</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>-0.005904</v>
+        <v>-0.0049095</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.0158222</v>
+        <v>0.0149687</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>-21.9099</v>
+        <v>-19.14631</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>1.37039</v>
+        <v>1.370197</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1.830416</v>
+        <v>1.830424</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>63.01748</v>
+        <v>63.02205</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>38.42213</v>
+        <v>50.22321</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.0155486</v>
+        <v>0.0146794</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>-0.0072393</v>
+        <v>-0.005904</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.0171513</v>
+        <v>0.0158222</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>-24.96623</v>
+        <v>-21.9099</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1.371037</v>
+        <v>1.37039</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1.830409</v>
+        <v>1.830416</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>63.01723</v>
+        <v>63.01748</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>31.25</v>
+        <v>38.42213</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>0.016455</v>
+        <v>0.0155486</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>-0.008394</v>
+        <v>-0.0072393</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.0184723</v>
+        <v>0.0171513</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>-27.02712</v>
+        <v>-24.96623</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>1.370941</v>
+        <v>1.371037</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1.83043</v>
+        <v>1.830409</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>63.02502</v>
+        <v>63.01723</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>24.93351</v>
+        <v>31.25</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>0.0177621</v>
+        <v>0.016455</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>-0.0097371</v>
+        <v>-0.008394</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.0202559</v>
+        <v>0.0184723</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>-28.73141</v>
+        <v>-27.02712</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1.370726</v>
+        <v>1.370941</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1.830417</v>
+        <v>1.83043</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>63.02263</v>
+        <v>63.02502</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>19.86229</v>
+        <v>24.93351</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>0.0194624</v>
+        <v>0.0177621</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>-0.0111186</v>
+        <v>-0.0097371</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.0224145</v>
+        <v>0.0202559</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>-29.7387</v>
+        <v>-28.73141</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>1.37264</v>
+        <v>1.370726</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1.830428</v>
+        <v>1.830417</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>63.0245</v>
+        <v>63.02263</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>15.625</v>
+        <v>19.86229</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>0.0217271</v>
+        <v>0.0194624</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>-0.0124396</v>
+        <v>-0.0111186</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.0250362</v>
+        <v>0.0224145</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>-29.79273</v>
+        <v>-29.7387</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>1.371369</v>
+        <v>1.37264</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1.830389</v>
+        <v>1.830428</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>63.02415</v>
+        <v>63.0245</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>12.40079</v>
+        <v>15.625</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>0.0243202</v>
+        <v>0.0217271</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>-0.0133973</v>
+        <v>-0.0124396</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0.0277662</v>
+        <v>0.0250362</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-28.84904</v>
+        <v>-29.79273</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>1.372793</v>
+        <v>1.371369</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1.830431</v>
+        <v>1.830389</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>63.02318</v>
+        <v>63.02415</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>9.931139999999999</v>
+        <v>12.40079</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0.0271054</v>
+        <v>0.0243202</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>-0.0139035</v>
+        <v>-0.0133973</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.0304632</v>
+        <v>0.0277662</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>-27.15519</v>
+        <v>-28.84904</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>1.373632</v>
+        <v>1.372793</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1.830419</v>
+        <v>1.830431</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>63.03325</v>
+        <v>63.02318</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>7.944915</v>
+        <v>9.931139999999999</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>0.0299782</v>
+        <v>0.0271054</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>-0.0138895</v>
+        <v>-0.0139035</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.0330395</v>
+        <v>0.0304632</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>-24.85932</v>
+        <v>-27.15519</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>1.37405</v>
+        <v>1.373632</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1.830404</v>
+        <v>1.830419</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>63.03027</v>
+        <v>63.03325</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>6.317385</v>
+        <v>7.944915</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0.0328637</v>
+        <v>0.0299782</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>-0.0133419</v>
+        <v>-0.0138895</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.0354687</v>
+        <v>0.0330395</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>-22.09604</v>
+        <v>-24.85932</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1.372868</v>
+        <v>1.37405</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1.830405</v>
+        <v>1.830404</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>63.02437</v>
+        <v>63.03027</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>5.008013</v>
+        <v>6.317385</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>0.035464</v>
+        <v>0.0328637</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>-0.0123183</v>
+        <v>-0.0133419</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.0375425</v>
+        <v>0.0354687</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-19.15452</v>
+        <v>-22.09604</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>1.373556</v>
+        <v>1.372868</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1.8304</v>
+        <v>1.830405</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>63.00269</v>
+        <v>63.02437</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>3.945707</v>
+        <v>5.008013</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>0.0376907</v>
+        <v>0.035464</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>-0.0109602</v>
+        <v>-0.0123183</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.0392519</v>
+        <v>0.0375425</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>-16.21413</v>
+        <v>-19.15452</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>1.372732</v>
+        <v>1.373556</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1.830412</v>
+        <v>1.8304</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>63.01316</v>
+        <v>63.00269</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>3.158693</v>
+        <v>3.945707</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>0.0393198</v>
+        <v>0.0376907</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>-0.009601800000000001</v>
+        <v>-0.0109602</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.0404752</v>
+        <v>0.0392519</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>-13.72289</v>
+        <v>-16.21413</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>1.372643</v>
+        <v>1.372732</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1.830403</v>
+        <v>1.830412</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>63.02723</v>
+        <v>63.01316</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>2.504006</v>
+        <v>3.158693</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>0.0406334</v>
+        <v>0.0393198</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>-0.008178599999999999</v>
+        <v>-0.009601800000000001</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0.0414483</v>
+        <v>0.0404752</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>-11.38026</v>
+        <v>-13.72289</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1.371627</v>
+        <v>1.372643</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1.83041</v>
+        <v>1.830403</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>63.02073</v>
+        <v>63.02723</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>1.998082</v>
+        <v>2.504006</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>0.0415942</v>
+        <v>0.0406334</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>-0.0069077</v>
+        <v>-0.008178599999999999</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>0.0421639</v>
+        <v>0.0414483</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>-9.429233</v>
+        <v>-11.38026</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>1.371141</v>
+        <v>1.371627</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1.830421</v>
+        <v>1.83041</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>63.01786</v>
+        <v>63.02073</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>1.584686</v>
+        <v>1.998082</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>0.0423216</v>
+        <v>0.0415942</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>-0.0057173</v>
+        <v>-0.0069077</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>0.042706</v>
+        <v>0.0421639</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>-7.693643</v>
+        <v>-9.429233</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>1.369162</v>
+        <v>1.371141</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1.830413</v>
+        <v>1.830421</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>63.01844</v>
+        <v>63.01786</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>1.266892</v>
+        <v>1.584686</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>0.0428405</v>
+        <v>0.0423216</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>-0.0047638</v>
+        <v>-0.0057173</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>0.0431046</v>
+        <v>0.042706</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>-6.345082</v>
+        <v>-7.693643</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>1.367385</v>
+        <v>1.369162</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1.830404</v>
+        <v>1.830413</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>63.00719</v>
+        <v>63.01844</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>0.999041</v>
+        <v>1.266892</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>0.0432582</v>
+        <v>0.0428405</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>-0.0038614</v>
+        <v>-0.0047638</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0.0434302</v>
+        <v>0.0431046</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>-5.100992</v>
+        <v>-6.345082</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>1.366262</v>
+        <v>1.367385</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1.830411</v>
+        <v>1.830404</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>63.01472</v>
+        <v>63.00719</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>0.7923428</v>
+        <v>0.999041</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>0.043472</v>
+        <v>0.0432582</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>-0.0031821</v>
+        <v>-0.0038614</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0.0435883</v>
+        <v>0.0434302</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>-4.186546</v>
+        <v>-5.100992</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>1.365449</v>
+        <v>1.366262</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1.830414</v>
+        <v>1.830411</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>63.00141</v>
+        <v>63.01472</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>0.6334459</v>
+        <v>0.7923428</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>0.0437065</v>
+        <v>0.043472</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>-0.002618</v>
+        <v>-0.0031821</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0.0437848</v>
+        <v>0.0435883</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>-3.427873</v>
+        <v>-4.186546</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>1.363699</v>
+        <v>1.365449</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1.83041</v>
+        <v>1.830414</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>63.00561</v>
+        <v>63.00141</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>0.5040323</v>
+        <v>0.6334459</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>0.0438847</v>
+        <v>0.0437065</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>-0.0020671</v>
+        <v>-0.002618</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0.0439334</v>
+        <v>0.0437848</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>-2.696767</v>
+        <v>-3.427873</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>1.361538</v>
+        <v>1.363699</v>
       </c>
       <c r="I55" s="2" t="n">
         <v>1.83041</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>63.00078</v>
+        <v>63.00561</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>0.400641</v>
+        <v>0.5040323</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>0.0440313</v>
+        <v>0.0438847</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>-0.0017212</v>
+        <v>-0.0020671</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.0440649</v>
+        <v>0.0439334</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>-2.238531</v>
+        <v>-2.696767</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>1.357276</v>
+        <v>1.361538</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1.830416</v>
+        <v>1.83041</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>62.97523</v>
+        <v>63.00078</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>0.316723</v>
+        <v>0.400641</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>0.0441978</v>
+        <v>0.0440313</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>-0.0014102</v>
+        <v>-0.0017212</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0.0442203</v>
+        <v>0.0440649</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>-1.827446</v>
+        <v>-2.238531</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>1.352211</v>
+        <v>1.357276</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1.830411</v>
+        <v>1.830416</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>62.96198</v>
+        <v>62.97523</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>0.2520161</v>
+        <v>0.316723</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>0.0444092</v>
+        <v>0.0441978</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>-0.0011583</v>
+        <v>-0.0014102</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0.0444243</v>
+        <v>0.0442203</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-1.494055</v>
+        <v>-1.827446</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1.350593</v>
+        <v>1.352211</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1.830414</v>
+        <v>1.830411</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>62.98516</v>
+        <v>62.96198</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>0.2003205</v>
+        <v>0.2520161</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>0.0443324</v>
+        <v>0.0444092</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>-0.0009338</v>
+        <v>-0.0011583</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.0443422</v>
+        <v>0.0444243</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-1.206635</v>
+        <v>-1.494055</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>1.353903</v>
+        <v>1.350593</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1.830407</v>
+        <v>1.830414</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>63.03751</v>
+        <v>62.98516</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>0.1588983</v>
+        <v>0.2003205</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>0.0443534</v>
+        <v>0.0443324</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>-0.0007618</v>
+        <v>-0.0009338</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0.0443599</v>
+        <v>0.0443422</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>-0.983971</v>
+        <v>-1.206635</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>1.350055</v>
+        <v>1.353903</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1.830409</v>
+        <v>1.830407</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>63.05511</v>
+        <v>63.03751</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>0.1260081</v>
+        <v>0.1588983</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>0.0443445</v>
+        <v>0.0443534</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>-0.0006395</v>
+        <v>-0.0007618</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0.0443491</v>
+        <v>0.0443599</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>-0.826273</v>
+        <v>-0.983971</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>1.351126</v>
+        <v>1.350055</v>
       </c>
       <c r="I61" s="2" t="n">
         <v>1.830409</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>63.08811</v>
+        <v>63.05511</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>0.1260081</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>0.0443445</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>-0.0006395</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>0.0443491</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>-0.826273</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>1.351126</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>1.830409</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>63.08811</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="B62" s="2" t="n">
+      <c r="B63" s="2" t="n">
         <v>0.1001603</v>
       </c>
-      <c r="C62" s="2" t="n">
+      <c r="C63" s="2" t="n">
         <v>0.0446354</v>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="D63" s="2" t="n">
         <v>-0.0005549</v>
       </c>
-      <c r="E62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="2" t="n">
+      <c r="E63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="2" t="n">
         <v>0.0446388</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>-0.7122211000000001</v>
       </c>
-      <c r="H62" s="2" t="n">
+      <c r="H63" s="2" t="n">
         <v>1.347761</v>
       </c>
-      <c r="I62" s="2" t="n">
+      <c r="I63" s="2" t="n">
         <v>1.830417</v>
       </c>
-      <c r="J62" s="2" t="n">
+      <c r="J63" s="2" t="n">
         <v>63.10437</v>
       </c>
     </row>

--- a/outputs/EISPOT_5mV_1,5A_#1.xlsx
+++ b/outputs/EISPOT_5mV_1,5A_#1.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>points/decade</t>
+          <t>puntos/década</t>
         </is>
       </c>
     </row>
